--- a/data/trans_orig/P43C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43C-Estudios-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2007</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2007 (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>522</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>521304</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>487539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>557534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>486338</t>
+          <t>487539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>556093</t>
+          <t>557534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>521304</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>486338</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>556093</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>40,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>37,88%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>43,32%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>739</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>762500</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>726270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>796265</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>727711</t>
+          <t>726270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>797466</t>
+          <t>796265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>762500</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>727711</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>797466</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>59,39%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>56,68%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1283804</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1283804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1283804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1283804</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1283804</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1283804</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>913</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944675</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>906391</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>981937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>908653</t>
+          <t>906391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>981723</t>
+          <t>981937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>913</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>944675</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>908653</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>981723</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>60,12%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>57,83%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>62,48%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>626601</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>589339</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>664885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>589553</t>
+          <t>589339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>662623</t>
+          <t>664885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>626601</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>589553</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>662623</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>37,52%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>42,17%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1571276</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1571276</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1571276</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1571276</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1571276</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1571276</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324369</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>302810</t>
+          <t>303832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>343807</t>
+          <t>342733</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>324369</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>302810</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>343807</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>72,84%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147601</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128163</t>
+          <t>129237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>169160</t>
+          <t>168138</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>147601</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>128163</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>169160</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>31,27%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>448</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>471970</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>471970</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>471970</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1790349</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1732279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1846842</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1729293</t>
+          <t>1732279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1845045</t>
+          <t>1846842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1790349</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1729293</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1845045</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>51,98%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>55,46%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1536701</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1480208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1594771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1482005</t>
+          <t>1480208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1597757</t>
+          <t>1594771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1536701</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1482005</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1597757</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>46,19%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>44,54%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>48,02%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3327050</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3327050</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3327050</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3247</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3327050</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3327050</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3327050</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2090,13 +1610,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2110,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2129,25 +1648,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2012</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2012 (tasa de respuesta: 98,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +1670,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2167,17 +1679,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2248,41 +1749,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2305,13 +1771,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2326,37 +1785,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>658</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>704584</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>664456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>739377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>665022</t>
+          <t>664456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>737574</t>
+          <t>739377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,47 +1845,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>704584</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>665022</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>737574</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>53,44%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>50,44%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -2439,37 +1863,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>571</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>613785</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>578992</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>653913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>580795</t>
+          <t>578992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>653347</t>
+          <t>653913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,47 +1923,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>613785</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>580795</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>653347</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>46,56%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>44,05%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>49,56%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -2552,37 +1941,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1318369</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1318369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1318369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2616,41 +2005,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1318369</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1318369</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1318369</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2669,37 +2023,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1237529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1197328</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1202368</t>
+          <t>1197328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1276610</t>
+          <t>1273448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,47 +2083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1136</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1237529</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1202368</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1276610</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>68,97%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>73,23%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -2782,37 +2101,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>485</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505808</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>469889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466727</t>
+          <t>469889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>540969</t>
+          <t>546009</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,47 +2161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>505808</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>466727</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>540969</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -2895,37 +2179,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1743337</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1743337</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1743337</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2959,41 +2243,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1621</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1743337</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1743337</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1743337</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3012,37 +2261,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347893</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>329006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>327496</t>
+          <t>329006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>365683</t>
+          <t>366523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,47 +2321,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>347893</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>327496</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>365683</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>76,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>71,73%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -3125,37 +2339,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108676</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127563</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90886</t>
+          <t>90046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129073</t>
+          <t>127563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,47 +2399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>108676</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>90886</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>129073</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -3238,37 +2417,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>456569</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>456569</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>456569</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3302,41 +2481,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>456569</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>456569</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>456569</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3355,37 +2499,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2290006</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2234574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2352384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2233729</t>
+          <t>2234574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2352220</t>
+          <t>2352384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,45 +2559,10 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>66,86%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2290006</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2233729</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2352220</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>65,09%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>63,49%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>66,86%</t>
         </is>
@@ -3468,37 +2577,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1228269</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1165891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1283701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1166055</t>
+          <t>1165891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1284546</t>
+          <t>1283701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3533,42 +2642,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1156</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1228269</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1166055</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1284546</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>34,91%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -3581,37 +2655,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3518275</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3518275</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3518275</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3645,41 +2719,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3518275</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3518275</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3518275</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3693,13 +2732,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -3713,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3732,25 +2770,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2016</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2016 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +2792,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3770,17 +2801,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3851,41 +2871,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3908,13 +2893,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3929,37 +2907,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>502579</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>470322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>470096</t>
+          <t>470322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>537984</t>
+          <t>536415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,47 +2967,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>502579</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>470096</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>537984</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>51,42%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>55,04%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -4042,37 +2985,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>417</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474854</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>507111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>439449</t>
+          <t>441018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>507337</t>
+          <t>507111</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,47 +3045,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>474854</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>439449</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>507337</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>48,58%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>44,96%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>51,91%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -4155,37 +3063,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>877</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>977433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>977433</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>977433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4219,41 +3127,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>977433</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>977433</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>977433</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4272,37 +3145,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1306182</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1264784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1349395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1263487</t>
+          <t>1264784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1349340</t>
+          <t>1349395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,45 +3205,10 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>68,47%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1306182</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1263487</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1349340</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>66,28%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>64,11%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>68,47%</t>
         </is>
@@ -4385,37 +3223,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>638</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>664507</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>621294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>705905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>621349</t>
+          <t>621294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>707202</t>
+          <t>705905</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,42 +3288,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>664507</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>621349</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>707202</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>33,72%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>35,89%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -4498,37 +3301,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1970689</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1970689</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1970689</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4562,41 +3365,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1970689</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1970689</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1970689</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4615,37 +3383,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>401</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424088</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>442763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>404977</t>
+          <t>403495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>444256</t>
+          <t>442763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,47 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>424088</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>404977</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>444256</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>77,51%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>74,02%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>81,2%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -4728,37 +3461,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123050</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102882</t>
+          <t>104375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142161</t>
+          <t>143643</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,47 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>123050</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>102882</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>142161</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>22,49%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>25,98%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -4841,37 +3539,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>524</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>547138</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>547138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>547138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4905,41 +3603,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>547138</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>547138</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>547138</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4958,37 +3621,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2232850</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2174460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2289704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2174260</t>
+          <t>2174460</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2290815</t>
+          <t>2289704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,42 +3686,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2232850</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2174260</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2290815</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>63,88%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>62,21%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>65,54%</t>
+          <t>65,51%</t>
         </is>
       </c>
     </row>
@@ -5071,37 +3699,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1262410</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1205556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1320800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1204445</t>
+          <t>1205556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1321000</t>
+          <t>1320800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,45 +3759,10 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>37,79%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1178</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1262410</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1204445</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1321000</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>36,12%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>34,46%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>37,79%</t>
         </is>
@@ -5184,37 +3777,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3495260</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3495260</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3495260</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5248,41 +3841,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3495260</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3495260</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3495260</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5296,13 +3854,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -5316,7 +3873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5335,25 +3892,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2023</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2023 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +3914,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5373,17 +3923,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5454,41 +3993,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5511,13 +4015,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5532,37 +4029,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>532</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285746</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +4074,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>268250</t>
+          <t>267050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>306767</t>
+          <t>305588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,47 +4089,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>285746</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>268250</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>306767</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>44,34%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>50,71%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -5645,37 +4107,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>623</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319237</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>299395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +4152,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298216</t>
+          <t>299395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336733</t>
+          <t>337933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,47 +4167,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>319237</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>298216</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>336733</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>49,29%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>55,66%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -5758,37 +4185,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>604983</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>604983</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>604983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5822,41 +4249,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1155</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>604983</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>604983</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>604983</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5875,37 +4267,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>935424</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>597162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1087995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +4312,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>629192</t>
+          <t>597162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1085539</t>
+          <t>1087995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,47 +4327,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>935424</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>629192</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1085539</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>53,79%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>62,42%</t>
+          <t>62,56%</t>
         </is>
       </c>
     </row>
@@ -5988,37 +4345,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>789</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>803600</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>651029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1141862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +4390,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>653485</t>
+          <t>651029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1109832</t>
+          <t>1141862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,47 +4405,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>803600</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>653485</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1109832</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -6101,37 +4423,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1739024</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1739024</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1739024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6165,41 +4487,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1739024</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1739024</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1739024</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6218,37 +4505,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346682</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>328585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +4550,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>330026</t>
+          <t>328585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>364195</t>
+          <t>363047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,47 +4565,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>346682</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>330026</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>364195</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>75,37%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>71,75%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>79,18%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -6331,37 +4583,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113302</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +4628,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95789</t>
+          <t>96937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129958</t>
+          <t>131399</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,47 +4643,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>113302</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>95789</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>129958</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>28,25%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -6444,37 +4661,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>699</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>459984</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>459984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>459984</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6508,41 +4725,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>459984</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>459984</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>459984</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6561,37 +4743,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1567852</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1174074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1718188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +4788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1213073</t>
+          <t>1174074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1718825</t>
+          <t>1718188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,47 +4803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2413</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1567852</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1213073</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1718825</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>43,26%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>61,3%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -6674,37 +4821,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1236139</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1085803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1629917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +4866,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1085166</t>
+          <t>1085803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1590918</t>
+          <t>1629917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,47 +4881,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1236139</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1085166</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1590918</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>44,08%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>38,7%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>56,74%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -6787,37 +4899,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2803991</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2803991</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2803991</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6851,41 +4963,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3981</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2803991</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2803991</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2803991</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6899,13 +4976,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P43C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43C-Estudios-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>487539</t>
+          <t>488857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>557534</t>
+          <t>557364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>487539</t>
+          <t>488857</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>557534</t>
+          <t>557364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>726270</t>
+          <t>726440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>796265</t>
+          <t>794947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>726270</t>
+          <t>726440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>796265</t>
+          <t>794947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>906391</t>
+          <t>904195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>981937</t>
+          <t>983552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>906391</t>
+          <t>904195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>981937</t>
+          <t>983552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>589339</t>
+          <t>587724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>664885</t>
+          <t>667081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>589339</t>
+          <t>587724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>664885</t>
+          <t>667081</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>303832</t>
+          <t>304218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342733</t>
+          <t>345113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>303832</t>
+          <t>304218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>342733</t>
+          <t>345113</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129237</t>
+          <t>126857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168138</t>
+          <t>167752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129237</t>
+          <t>126857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168138</t>
+          <t>167752</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1732279</t>
+          <t>1728222</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1846842</t>
+          <t>1846242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1732279</t>
+          <t>1728222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1846842</t>
+          <t>1846242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1480208</t>
+          <t>1480808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1594771</t>
+          <t>1598828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1480208</t>
+          <t>1480808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1594771</t>
+          <t>1598828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>664456</t>
+          <t>667543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>739377</t>
+          <t>742918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>664456</t>
+          <t>667543</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>739377</t>
+          <t>742918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,35%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>578992</t>
+          <t>575451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>653913</t>
+          <t>650826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>578992</t>
+          <t>575451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>653913</t>
+          <t>650826</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1197328</t>
+          <t>1199087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1273448</t>
+          <t>1273126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1197328</t>
+          <t>1199087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1273448</t>
+          <t>1273126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469889</t>
+          <t>470211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>546009</t>
+          <t>544250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469889</t>
+          <t>470211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>546009</t>
+          <t>544250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>329006</t>
+          <t>327521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>366523</t>
+          <t>365800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>329006</t>
+          <t>327521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>366523</t>
+          <t>365800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90046</t>
+          <t>90769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127563</t>
+          <t>129048</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90046</t>
+          <t>90769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127563</t>
+          <t>129048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2234574</t>
+          <t>2234860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2352384</t>
+          <t>2344940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2234574</t>
+          <t>2234860</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2352384</t>
+          <t>2344940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1165891</t>
+          <t>1173335</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1283701</t>
+          <t>1283415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1165891</t>
+          <t>1173335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1283701</t>
+          <t>1283415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>470322</t>
+          <t>469029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>536415</t>
+          <t>534609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>470322</t>
+          <t>469029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>536415</t>
+          <t>534609</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441018</t>
+          <t>442824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>507111</t>
+          <t>508404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441018</t>
+          <t>442824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>507111</t>
+          <t>508404</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1264784</t>
+          <t>1263364</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1349395</t>
+          <t>1349156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1264784</t>
+          <t>1263364</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1349395</t>
+          <t>1349156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>621294</t>
+          <t>621533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>705905</t>
+          <t>707325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>621294</t>
+          <t>621533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>705905</t>
+          <t>707325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>403495</t>
+          <t>403145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>442763</t>
+          <t>441073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>403495</t>
+          <t>403145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>442763</t>
+          <t>441073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104375</t>
+          <t>106065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143643</t>
+          <t>143993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104375</t>
+          <t>106065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143643</t>
+          <t>143993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2174460</t>
+          <t>2171925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2289704</t>
+          <t>2288415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2174460</t>
+          <t>2171925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2289704</t>
+          <t>2288415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1205556</t>
+          <t>1206845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1320800</t>
+          <t>1323335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1205556</t>
+          <t>1206845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1320800</t>
+          <t>1323335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -4034,32 +4034,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>267050</t>
+          <t>283700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>305588</t>
+          <t>324867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4069,32 +4069,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267050</t>
+          <t>283700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>305588</t>
+          <t>324867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -4112,32 +4112,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>319237</t>
+          <t>355465</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>299395</t>
+          <t>334337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>337933</t>
+          <t>375504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4147,32 +4147,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>319237</t>
+          <t>355465</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299395</t>
+          <t>334337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337933</t>
+          <t>375504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,96%</t>
         </is>
       </c>
     </row>
@@ -4190,17 +4190,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>604983</t>
+          <t>659204</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>604983</t>
+          <t>659204</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>604983</t>
+          <t>659204</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4225,17 +4225,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>604983</t>
+          <t>659204</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>604983</t>
+          <t>659204</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>604983</t>
+          <t>659204</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,32 +4272,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>935424</t>
+          <t>916008</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>597162</t>
+          <t>882092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1087995</t>
+          <t>956316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4307,32 +4307,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>935424</t>
+          <t>916008</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>597162</t>
+          <t>882092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1087995</t>
+          <t>956316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -4350,32 +4350,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>803600</t>
+          <t>690826</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>651029</t>
+          <t>650518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1141862</t>
+          <t>724742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4385,32 +4385,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>803600</t>
+          <t>690826</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>651029</t>
+          <t>650518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1141862</t>
+          <t>724742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1739024</t>
+          <t>1606834</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1739024</t>
+          <t>1606834</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1739024</t>
+          <t>1606834</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1739024</t>
+          <t>1606834</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1739024</t>
+          <t>1606834</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1739024</t>
+          <t>1606834</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4510,32 +4510,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386803</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>328585</t>
+          <t>368121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>363047</t>
+          <t>404879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4545,32 +4545,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386803</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>328585</t>
+          <t>368121</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>363047</t>
+          <t>404879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -4588,32 +4588,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>113302</t>
+          <t>122997</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96937</t>
+          <t>104921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131399</t>
+          <t>141679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113302</t>
+          <t>122997</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96937</t>
+          <t>104921</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131399</t>
+          <t>141679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -4666,17 +4666,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>459984</t>
+          <t>509800</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>459984</t>
+          <t>509800</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>459984</t>
+          <t>509800</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>459984</t>
+          <t>509800</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>459984</t>
+          <t>509800</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>459984</t>
+          <t>509800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4748,32 +4748,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1567852</t>
+          <t>1606551</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1174074</t>
+          <t>1560800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1718188</t>
+          <t>1652936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4783,32 +4783,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1567852</t>
+          <t>1606551</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1174074</t>
+          <t>1560800</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1718188</t>
+          <t>1652936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -4826,32 +4826,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1236139</t>
+          <t>1169287</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1085803</t>
+          <t>1122902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1629917</t>
+          <t>1215038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,32 +4861,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1236139</t>
+          <t>1169287</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1085803</t>
+          <t>1122902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1629917</t>
+          <t>1215038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -4904,17 +4904,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2803991</t>
+          <t>2775838</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2803991</t>
+          <t>2775838</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2803991</t>
+          <t>2775838</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2803991</t>
+          <t>2775838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2803991</t>
+          <t>2775838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2803991</t>
+          <t>2775838</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
